--- a/scenarios/DRY_COWS.xlsx
+++ b/scenarios/DRY_COWS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="CattleHerd" sheetId="4" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="36">
   <si>
     <t>parameter</t>
   </si>
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>all other feeds reduced proportionally</t>
+  </si>
+  <si>
+    <t>new</t>
   </si>
 </sst>
 </file>
@@ -134,7 +137,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +168,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -186,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -194,9 +211,13 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,14 +555,14 @@
       <c r="G2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="11">
         <f>K2</f>
         <v>9452.1428570000007</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="11">
         <v>10025.4</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="12">
         <v>9452.1428570000007</v>
       </c>
       <c r="L2" t="s">
@@ -561,14 +582,14 @@
       <c r="G3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="11">
         <f>K3</f>
         <v>8631.0214290000004</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="11">
         <v>9367.2000000000007</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="12">
         <v>8631.0214290000004</v>
       </c>
       <c r="L3" t="s">
@@ -595,7 +616,7 @@
       <c r="J5">
         <v>13.2</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="13">
         <v>14</v>
       </c>
       <c r="L5" t="s">
@@ -622,7 +643,7 @@
       <c r="J6">
         <v>12.9</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="13">
         <v>14</v>
       </c>
       <c r="L6" t="s">
@@ -649,7 +670,7 @@
       <c r="J8">
         <v>37.1</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="9">
         <v>35.4</v>
       </c>
       <c r="L8" t="s">
@@ -676,7 +697,7 @@
       <c r="J9">
         <v>36.1</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="9">
         <v>33.5</v>
       </c>
       <c r="L9" t="s">
@@ -698,15 +719,18 @@
       <c r="G11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="7">
-        <f>J11</f>
+      <c r="H11" s="4">
+        <f>K11</f>
         <v>651.52821361702138</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="4">
         <v>651.52821361702138</v>
       </c>
-      <c r="K11" s="4"/>
+      <c r="K11" s="10">
+        <f>J11</f>
+        <v>651.52821361702138</v>
+      </c>
       <c r="L11" t="s">
         <v>26</v>
       </c>
@@ -764,7 +788,7 @@
       <c r="J14" s="1">
         <v>6.6079520088655128</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="9">
         <v>16.5</v>
       </c>
     </row>
@@ -781,7 +805,7 @@
       <c r="G15" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="7">
         <f>(1 / (100 - J$14)) * (1 - K$14/100) * 100</f>
         <v>0.89408040401819311</v>
       </c>
@@ -818,7 +842,7 @@
       <c r="J16" s="1">
         <v>6.4615074492035101</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="9">
         <v>16.5</v>
       </c>
     </row>
@@ -841,7 +865,7 @@
       <c r="G17" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <f>(1 / (100 - J$16)) * (1 - K$16/100) * 100</f>
         <v>0.89268062508763379</v>
       </c>
@@ -899,8 +923,8 @@
       <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>18</v>
+      <c r="K1" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -932,7 +956,7 @@
       <c r="J2" s="2">
         <v>20</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="9">
         <v>50</v>
       </c>
       <c r="L2" t="s">

--- a/scenarios/DRY_COWS.xlsx
+++ b/scenarios/DRY_COWS.xlsx
@@ -783,13 +783,13 @@
       </c>
       <c r="H14" s="1">
         <f>K14</f>
-        <v>16.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="J14" s="1">
         <v>6.6079520088655128</v>
       </c>
       <c r="K14" s="9">
-        <v>16.5</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -807,7 +807,7 @@
       </c>
       <c r="H15" s="7">
         <f>(1 / (100 - J$14)) * (1 - K$14/100) * 100</f>
-        <v>0.89408040401819311</v>
+        <v>0.98188231195770437</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>34</v>
@@ -837,13 +837,13 @@
       </c>
       <c r="H16" s="1">
         <f>K16</f>
-        <v>16.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="J16" s="1">
         <v>6.4615074492035101</v>
       </c>
       <c r="K16" s="9">
-        <v>16.5</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -867,7 +867,7 @@
       </c>
       <c r="H17" s="7">
         <f>(1 / (100 - J$16)) * (1 - K$16/100) * 100</f>
-        <v>0.89268062508763379</v>
+        <v>0.98034506970701829</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>34</v>
@@ -951,13 +951,13 @@
       </c>
       <c r="H2" s="4">
         <f>K2</f>
-        <v>50</v>
+        <v>62.2</v>
       </c>
       <c r="J2" s="2">
         <v>20</v>
       </c>
       <c r="K2" s="9">
-        <v>50</v>
+        <v>62.2</v>
       </c>
       <c r="L2" t="s">
         <v>27</v>

--- a/scenarios/DRY_COWS.xlsx
+++ b/scenarios/DRY_COWS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="40">
   <si>
     <t>parameter</t>
   </si>
@@ -76,9 +76,6 @@
     <t>recruitment_rate</t>
   </si>
   <si>
-    <t>ret.</t>
-  </si>
-  <si>
     <t>cattle</t>
   </si>
   <si>
@@ -128,6 +125,21 @@
   </si>
   <si>
     <t>new</t>
+  </si>
+  <si>
+    <t>share of cows</t>
+  </si>
+  <si>
+    <t>conv.</t>
+  </si>
+  <si>
+    <t>org.</t>
+  </si>
+  <si>
+    <t>months as cow</t>
+  </si>
+  <si>
+    <t># calves</t>
   </si>
 </sst>
 </file>
@@ -203,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -218,6 +230,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -518,7 +534,7 @@
         <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>8</v>
@@ -539,7 +555,7 @@
         <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -566,7 +582,7 @@
         <v>9452.1428570000007</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -593,7 +609,7 @@
         <v>8631.0214290000004</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -611,16 +627,17 @@
       </c>
       <c r="H5" s="4">
         <f>K5</f>
-        <v>14</v>
+        <v>13.983749999999997</v>
       </c>
       <c r="J5">
         <v>13.2</v>
       </c>
       <c r="K5" s="13">
-        <v>14</v>
+        <f>12 / (K23 / (K21/12))</f>
+        <v>13.983749999999997</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -638,16 +655,17 @@
       </c>
       <c r="H6" s="4">
         <f>K6</f>
-        <v>14</v>
+        <v>13.994545454545452</v>
       </c>
       <c r="J6">
         <v>12.9</v>
       </c>
       <c r="K6" s="13">
-        <v>14</v>
+        <f>12 / (K24 / (K22/12))</f>
+        <v>13.994545454545452</v>
       </c>
       <c r="L6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -674,7 +692,7 @@
         <v>35.4</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -701,7 +719,7 @@
         <v>33.5</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -714,7 +732,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>2</v>
@@ -732,7 +750,7 @@
         <v>651.52821361702138</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M11" s="6"/>
     </row>
@@ -751,7 +769,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -803,14 +821,14 @@
         <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H15" s="7">
         <f>(1 / (100 - J$14)) * (1 - K$14/100) * 100</f>
         <v>0.98188231195770437</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -821,7 +839,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -846,7 +864,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -854,7 +872,7 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -863,14 +881,93 @@
         <v>6</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H17" s="7">
         <f>(1 / (100 - J$16)) * (1 - K$16/100) * 100</f>
         <v>0.98034506970701829</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H19" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I20" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H21" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" s="1">
+        <v>32</v>
+      </c>
+      <c r="K21" s="13">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="1">
+        <v>33</v>
+      </c>
+      <c r="K22" s="13">
+        <v>35.799999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" t="s">
+        <v>36</v>
+      </c>
+      <c r="J23" s="1">
+        <f>(12/J5) * (J21/12)</f>
+        <v>2.4242424242424243</v>
+      </c>
+      <c r="K23" s="15">
+        <f>J23</f>
+        <v>2.4242424242424243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" s="1">
+        <f>(12/J6) * (J22/12)</f>
+        <v>2.558139534883721</v>
+      </c>
+      <c r="K24" s="15">
+        <f>J24</f>
+        <v>2.558139534883721</v>
       </c>
     </row>
   </sheetData>
@@ -897,7 +994,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
@@ -906,10 +1003,10 @@
         <v>8</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>0</v>
@@ -924,12 +1021,12 @@
         <v>16</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -938,29 +1035,29 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="4">
         <f>K2</f>
-        <v>62.2</v>
+        <v>62.21</v>
       </c>
       <c r="J2" s="2">
         <v>20</v>
       </c>
       <c r="K2" s="9">
-        <v>62.2</v>
+        <v>62.21</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios/DRY_COWS.xlsx
+++ b/scenarios/DRY_COWS.xlsx
@@ -1,26 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960452A7-CA25-48A4-B2CE-83DC4A38C198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CattleHerd" sheetId="4" r:id="rId1"/>
     <sheet name="FeedMgmt" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="39">
   <si>
     <t>parameter</t>
   </si>
@@ -125,9 +137,6 @@
   </si>
   <si>
     <t>new</t>
-  </si>
-  <si>
-    <t>share of cows</t>
   </si>
   <si>
     <t>conv.</t>
@@ -145,7 +154,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -215,16 +224,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -513,8 +520,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -526,7 +533,7 @@
     <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -558,7 +565,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -571,21 +578,22 @@
       <c r="G2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="9">
         <f>K2</f>
-        <v>9452.1428570000007</v>
-      </c>
-      <c r="J2" s="11">
-        <v>10025.4</v>
-      </c>
-      <c r="K2" s="12">
-        <v>9452.1428570000007</v>
+        <v>9087.2571428571428</v>
+      </c>
+      <c r="J2" s="9">
+        <v>9638</v>
+      </c>
+      <c r="K2" s="10">
+        <f>J2/(K19/J19)</f>
+        <v>9087.2571428571428</v>
       </c>
       <c r="L2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -598,21 +606,22 @@
       <c r="G3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="9">
         <f>K3</f>
-        <v>8631.0214290000004</v>
-      </c>
-      <c r="J3" s="11">
-        <v>9367.2000000000007</v>
-      </c>
-      <c r="K3" s="12">
-        <v>8631.0214290000004</v>
+        <v>8297.4642857142862</v>
+      </c>
+      <c r="J3" s="9">
+        <v>9005</v>
+      </c>
+      <c r="K3" s="10">
+        <f>J3/(K20/J20)</f>
+        <v>8297.4642857142862</v>
       </c>
       <c r="L3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -627,20 +636,19 @@
       </c>
       <c r="H5" s="4">
         <f>K5</f>
-        <v>13.983749999999997</v>
+        <v>14</v>
       </c>
       <c r="J5">
         <v>13.2</v>
       </c>
-      <c r="K5" s="13">
-        <f>12 / (K23 / (K21/12))</f>
-        <v>13.983749999999997</v>
+      <c r="K5" s="11">
+        <v>14</v>
       </c>
       <c r="L5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -655,20 +663,19 @@
       </c>
       <c r="H6" s="4">
         <f>K6</f>
-        <v>13.994545454545452</v>
+        <v>14</v>
       </c>
       <c r="J6">
         <v>12.9</v>
       </c>
-      <c r="K6" s="13">
-        <f>12 / (K24 / (K22/12))</f>
-        <v>13.994545454545452</v>
+      <c r="K6" s="11">
+        <v>14</v>
       </c>
       <c r="L6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -683,19 +690,20 @@
       </c>
       <c r="H8" s="4">
         <f>K8</f>
-        <v>35.4</v>
+        <v>35.357142857142861</v>
       </c>
       <c r="J8">
         <v>37.1</v>
       </c>
-      <c r="K8" s="9">
-        <v>35.4</v>
+      <c r="K8" s="11">
+        <f>12/K19*100</f>
+        <v>35.357142857142861</v>
       </c>
       <c r="L8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -710,19 +718,20 @@
       </c>
       <c r="H9" s="4">
         <f>K9</f>
-        <v>33.5</v>
+        <v>33.506493506493506</v>
       </c>
       <c r="J9">
         <v>36.1</v>
       </c>
-      <c r="K9" s="9">
-        <v>33.5</v>
+      <c r="K9" s="11">
+        <f>12/K20*100</f>
+        <v>33.506493506493506</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -745,16 +754,15 @@
       <c r="J11" s="4">
         <v>651.52821361702138</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="8">
         <f>J11</f>
         <v>651.52821361702138</v>
       </c>
       <c r="L11" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -765,9 +773,8 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="4"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>31</v>
       </c>
@@ -781,9 +788,8 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="4"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -801,16 +807,16 @@
       </c>
       <c r="H14" s="1">
         <f>K14</f>
-        <v>8.3000000000000007</v>
+        <v>9.6</v>
       </c>
       <c r="J14" s="1">
         <v>6.6079520088655128</v>
       </c>
-      <c r="K14" s="9">
-        <v>8.3000000000000007</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K14" s="7">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -823,15 +829,15 @@
       <c r="G15" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <f>(1 / (100 - J$14)) * (1 - K$14/100) * 100</f>
-        <v>0.98188231195770437</v>
+        <v>0.96796249728436712</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -855,13 +861,13 @@
       </c>
       <c r="H16" s="1">
         <f>K16</f>
-        <v>8.3000000000000007</v>
+        <v>9.6</v>
       </c>
       <c r="J16" s="1">
         <v>6.4615074492035101</v>
       </c>
-      <c r="K16" s="9">
-        <v>8.3000000000000007</v>
+      <c r="K16" s="7">
+        <v>9.6</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -883,90 +889,67 @@
       <c r="G17" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="6">
         <f>(1 / (100 - J$16)) * (1 - K$16/100) * 100</f>
-        <v>0.98034506970701829</v>
+        <v>0.96644704799906722</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" t="s">
         <v>35</v>
       </c>
-      <c r="I19" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="9">
-        <v>0.25</v>
+      <c r="J19" s="1">
+        <v>32</v>
+      </c>
+      <c r="K19" s="11">
+        <f>K5*K21</f>
+        <v>33.939393939393938</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
-        <v>37</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9">
-        <v>0.25</v>
+        <v>36</v>
+      </c>
+      <c r="J20" s="1">
+        <v>33</v>
+      </c>
+      <c r="K20" s="11">
+        <f>K6*K22</f>
+        <v>35.813953488372093</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H21" s="14" t="s">
+      <c r="H21" t="s">
         <v>38</v>
       </c>
       <c r="I21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J21" s="1">
-        <v>32</v>
+        <f>(12/J5) * (J19/12)</f>
+        <v>2.4242424242424243</v>
       </c>
       <c r="K21" s="13">
-        <v>33.9</v>
+        <f>J21</f>
+        <v>2.4242424242424243</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J22" s="1">
-        <v>33</v>
+        <f>(12/J6) * (J20/12)</f>
+        <v>2.558139534883721</v>
       </c>
       <c r="K22" s="13">
-        <v>35.799999999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H23" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" t="s">
-        <v>36</v>
-      </c>
-      <c r="J23" s="1">
-        <f>(12/J5) * (J21/12)</f>
-        <v>2.4242424242424243</v>
-      </c>
-      <c r="K23" s="15">
-        <f>J23</f>
-        <v>2.4242424242424243</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I24" t="s">
-        <v>37</v>
-      </c>
-      <c r="J24" s="1">
-        <f>(12/J6) * (J22/12)</f>
-        <v>2.558139534883721</v>
-      </c>
-      <c r="K24" s="15">
-        <f>J24</f>
+        <f>J22</f>
         <v>2.558139534883721</v>
       </c>
     </row>
@@ -977,7 +960,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1020,7 +1003,7 @@
       <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1048,13 +1031,13 @@
       </c>
       <c r="H2" s="4">
         <f>K2</f>
-        <v>62.21</v>
+        <v>57</v>
       </c>
       <c r="J2" s="2">
-        <v>20</v>
-      </c>
-      <c r="K2" s="9">
-        <v>62.21</v>
+        <v>28</v>
+      </c>
+      <c r="K2" s="7">
+        <v>57</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>

--- a/scenarios/DRY_COWS.xlsx
+++ b/scenarios/DRY_COWS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960452A7-CA25-48A4-B2CE-83DC4A38C198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F55F7D-84E0-4E34-B54D-E38F0C85FA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="3150" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CattleHerd" sheetId="4" r:id="rId1"/>
@@ -85,9 +85,6 @@
     <t>orig.</t>
   </si>
   <si>
-    <t>recruitment_rate</t>
-  </si>
-  <si>
     <t>cattle</t>
   </si>
   <si>
@@ -149,6 +146,9 @@
   </si>
   <si>
     <t># calves</t>
+  </si>
+  <si>
+    <t>replacement_rate</t>
   </si>
 </sst>
 </file>
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>8</v>
@@ -562,7 +562,7 @@
         <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -590,7 +590,7 @@
         <v>9087.2571428571428</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -618,7 +618,7 @@
         <v>8297.4642857142862</v>
       </c>
       <c r="L3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -645,7 +645,7 @@
         <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -672,7 +672,7 @@
         <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -683,7 +683,7 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
         <v>2</v>
@@ -700,7 +700,7 @@
         <v>35.357142857142861</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -711,7 +711,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
         <v>2</v>
@@ -728,7 +728,7 @@
         <v>33.506493506493506</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -741,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>2</v>
@@ -759,7 +759,7 @@
         <v>651.52821361702138</v>
       </c>
       <c r="L11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -776,7 +776,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -827,14 +827,14 @@
         <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H15" s="6">
         <f>(1 / (100 - J$14)) * (1 - K$14/100) * 100</f>
         <v>0.96796249728436712</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -845,7 +845,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -887,22 +887,22 @@
         <v>6</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H17" s="6">
         <f>(1 / (100 - J$16)) * (1 - K$16/100) * 100</f>
         <v>0.96644704799906722</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H19" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J19" s="1">
         <v>32</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J20" s="1">
         <v>33</v>
@@ -926,10 +926,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J21" s="1">
         <f>(12/J5) * (J19/12)</f>
@@ -942,7 +942,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J22" s="1">
         <f>(12/J6) * (J20/12)</f>
@@ -977,7 +977,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
@@ -986,10 +986,10 @@
         <v>8</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>0</v>
@@ -1004,12 +1004,12 @@
         <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -1018,13 +1018,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
@@ -1040,7 +1040,7 @@
         <v>57</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios/DRY_COWS.xlsx
+++ b/scenarios/DRY_COWS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F55F7D-84E0-4E34-B54D-E38F0C85FA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96955571-46A3-4B74-9361-07C2AE172548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3150" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38505" yWindow="-2775" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CattleHerd" sheetId="4" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="40">
   <si>
     <t>parameter</t>
   </si>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>replacement_rate</t>
+  </si>
+  <si>
+    <t>&lt;-- Same %-unit increase as conventional</t>
   </si>
 </sst>
 </file>
@@ -158,7 +161,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +206,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -224,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -241,6 +252,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -586,7 +598,7 @@
         <v>9638</v>
       </c>
       <c r="K2" s="10">
-        <f>J2/(K19/J19)</f>
+        <f>J2/(K21/J21)</f>
         <v>9087.2571428571428</v>
       </c>
       <c r="L2" t="s">
@@ -614,7 +626,7 @@
         <v>9005</v>
       </c>
       <c r="K3" s="10">
-        <f>J3/(K20/J20)</f>
+        <f>J3/(K22/J22)</f>
         <v>8297.4642857142862</v>
       </c>
       <c r="L3" t="s">
@@ -696,7 +708,7 @@
         <v>37.1</v>
       </c>
       <c r="K8" s="11">
-        <f>12/K19*100</f>
+        <f>12/K21*100</f>
         <v>35.357142857142861</v>
       </c>
       <c r="L8" t="s">
@@ -724,7 +736,7 @@
         <v>36.1</v>
       </c>
       <c r="K9" s="11">
-        <f>12/K20*100</f>
+        <f>12/K22*100</f>
         <v>33.506493506493506</v>
       </c>
       <c r="L9" t="s">
@@ -793,6 +805,9 @@
       <c r="A14" t="s">
         <v>4</v>
       </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
@@ -820,6 +835,9 @@
       <c r="A15" t="s">
         <v>4</v>
       </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
@@ -842,10 +860,7 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -861,13 +876,17 @@
       </c>
       <c r="H16" s="1">
         <f>K16</f>
-        <v>9.6</v>
+        <v>13.789458206396507</v>
       </c>
       <c r="J16" s="1">
-        <v>6.4615074492035101</v>
-      </c>
-      <c r="K16" s="7">
-        <v>9.6</v>
+        <v>10.797410215262019</v>
+      </c>
+      <c r="K16" s="11">
+        <f>J16+(K14-J14)</f>
+        <v>13.789458206396507</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -875,10 +894,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -891,53 +907,85 @@
       </c>
       <c r="H17" s="6">
         <f>(1 / (100 - J$16)) * (1 - K$16/100) * 100</f>
-        <v>0.96644704799906722</v>
+        <v>0.96645783493108395</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" s="1">
+        <f>K18</f>
+        <v>9.6</v>
+      </c>
+      <c r="J18" s="1">
+        <v>6.4615074492035101</v>
+      </c>
+      <c r="K18" s="7">
+        <v>9.6</v>
+      </c>
+    </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H19" s="12" t="s">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="6">
+        <f>(1 / (100 - J$18)) * (1 - K$18/100) * 100</f>
+        <v>0.96644704799906722</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H21" s="12" t="s">
         <v>36</v>
-      </c>
-      <c r="I19" t="s">
-        <v>34</v>
-      </c>
-      <c r="J19" s="1">
-        <v>32</v>
-      </c>
-      <c r="K19" s="11">
-        <f>K5*K21</f>
-        <v>33.939393939393938</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I20" t="s">
-        <v>35</v>
-      </c>
-      <c r="J20" s="1">
-        <v>33</v>
-      </c>
-      <c r="K20" s="11">
-        <f>K6*K22</f>
-        <v>35.813953488372093</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H21" t="s">
-        <v>37</v>
       </c>
       <c r="I21" t="s">
         <v>34</v>
       </c>
       <c r="J21" s="1">
-        <f>(12/J5) * (J19/12)</f>
-        <v>2.4242424242424243</v>
-      </c>
-      <c r="K21" s="13">
-        <f>J21</f>
-        <v>2.4242424242424243</v>
+        <v>32</v>
+      </c>
+      <c r="K21" s="11">
+        <f>K5*K23</f>
+        <v>33.939393939393938</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -945,11 +993,39 @@
         <v>35</v>
       </c>
       <c r="J22" s="1">
-        <f>(12/J6) * (J20/12)</f>
+        <v>33</v>
+      </c>
+      <c r="K22" s="11">
+        <f>K6*K24</f>
+        <v>35.813953488372093</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="1">
+        <f>(12/J5) * (J21/12)</f>
+        <v>2.4242424242424243</v>
+      </c>
+      <c r="K23" s="13">
+        <f>J23</f>
+        <v>2.4242424242424243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="1">
+        <f>(12/J6) * (J22/12)</f>
         <v>2.558139534883721</v>
       </c>
-      <c r="K22" s="13">
-        <f>J22</f>
+      <c r="K24" s="13">
+        <f>J24</f>
         <v>2.558139534883721</v>
       </c>
     </row>
